--- a/AAII_Financials/Quarterly/TSM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TSM_QTR_FIN.xlsx
@@ -656,531 +656,543 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="22" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="23" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>39930200</v>
+      </c>
+      <c r="E8" s="3">
         <v>35462900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>33312900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>32473400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>31931100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>25222500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>26493600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>23919000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>20732300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>18535800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>20416800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>16989800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>15426900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>16673200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>19585400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>19013600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>16926900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>15395200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>13759100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>13497500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>12068700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>11553600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>11525700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>11933100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>10402200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>11187700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>11319000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>10508600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>8422900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>7672200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>9872500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>8682600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>7758800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>8251100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>8996100</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>8170800</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>6931000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>7627900</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>8551200</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>8491800</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>12889200</v>
+      </c>
+      <c r="E9" s="3">
         <v>11970200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>12550300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>13166800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>13213700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>10394300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>10862800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>10086200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>9708400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>8699200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>9588100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>7771600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>7078900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>7281600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>7400000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>7524400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>6929700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>6830300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>6513400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>6572600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>6030300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>5501600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>5303100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>5555900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>4888300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>5396300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>5637300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>5508600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>4799500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>4502600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>5169400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>4567900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>4047400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>4094400</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>4500300</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>4091100</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>3406400</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>3666300</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>4080100</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>4186000</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>27041000</v>
+      </c>
+      <c r="E10" s="3">
         <v>23492700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>20762600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>19306600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>18717300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>14828200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>15630800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>13832900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>11024000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>9836600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>10828600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>9218200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>8348000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>9391600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>12185400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>11489200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>9997200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>8564900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>7245700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>6924900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>6038400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>6052100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>6222600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>6377300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>5513900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>5791400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>5681700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>5000000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3623400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3169600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>4703100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>4114800</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>3711400</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>4156700</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>4495800</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>4079700</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>3524700</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>3961600</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>4471200</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>4305800</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1223,130 +1235,134 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>2299100</v>
+      </c>
+      <c r="E12" s="3">
         <v>2118700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2065400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>2091000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>2095500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1699400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1745900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1661900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1479300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1442100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1645300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1589100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1336800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1283600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1396000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1332700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1256500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1130100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1012300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1004700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1001200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>980500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>954500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>993800</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>833400</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>899400</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>914700</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>859600</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>747700</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>716200</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>807100</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>729900</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>661600</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>679500</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>687600</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>682100</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>617700</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>633000</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>650900</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>610600</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1467,101 +1483,104 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-1984700</v>
+      </c>
+      <c r="E14" s="3">
         <v>1300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-24500</v>
-      </c>
-      <c r="F14" s="3">
-        <v>500</v>
       </c>
       <c r="G14" s="3">
         <v>500</v>
       </c>
       <c r="H14" s="3">
+        <v>500</v>
+      </c>
+      <c r="I14" s="3">
         <v>6300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>12300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>3100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>3500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>3400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>4200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>4400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>4700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>300</v>
-      </c>
-      <c r="S14" s="3">
-        <v>400</v>
       </c>
       <c r="T14" s="3">
         <v>400</v>
       </c>
       <c r="U14" s="3">
+        <v>400</v>
+      </c>
+      <c r="V14" s="3">
         <v>100</v>
-      </c>
-      <c r="V14" s="3">
-        <v>-100</v>
       </c>
       <c r="W14" s="3">
         <v>-100</v>
       </c>
       <c r="X14" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
       </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>100</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>100</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE14" s="3">
         <v>100</v>
       </c>
       <c r="AF14" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG14" s="3">
         <v>-10600</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
       <c r="AH14" s="3">
         <v>0</v>
       </c>
@@ -1569,72 +1588,75 @@
         <v>0</v>
       </c>
       <c r="AJ14" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AK14" s="3">
         <v>-100</v>
       </c>
       <c r="AL14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AM14" s="3">
         <v>100</v>
       </c>
-      <c r="AM14" s="3">
-        <v>0</v>
-      </c>
       <c r="AN14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="3">
         <v>400</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>2200</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>6140800</v>
+      </c>
+      <c r="E15" s="3">
         <v>5082400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>5072500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>5248900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>6341200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>5188800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>5126200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>5226200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>5016900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>4899200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>4843600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>4506600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>3907100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>3547500</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>100</v>
       </c>
       <c r="R15" s="3">
         <v>100</v>
@@ -1643,28 +1665,28 @@
         <v>100</v>
       </c>
       <c r="T15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U15" s="3">
         <v>0</v>
       </c>
       <c r="V15" s="3">
+        <v>0</v>
+      </c>
+      <c r="W15" s="3">
         <v>400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>2000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>2300</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>700</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>100</v>
-      </c>
-      <c r="AA15" s="3">
-        <v>200</v>
       </c>
       <c r="AB15" s="3">
         <v>200</v>
@@ -1682,14 +1704,14 @@
         <v>200</v>
       </c>
       <c r="AG15" s="3">
+        <v>200</v>
+      </c>
+      <c r="AH15" s="3">
         <v>100</v>
       </c>
-      <c r="AH15" s="3" t="s">
+      <c r="AI15" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AI15" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
@@ -1711,8 +1733,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1752,252 +1777,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>15834600</v>
+      </c>
+      <c r="E17" s="3">
         <v>14857300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>15351800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>16048900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>16084300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>12988300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>13506700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>12560200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>11911400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>10747400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>11923900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>9902700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>8947500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>9093100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>9409000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>9390700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>8620600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>8379800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>8020200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>7931300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>7344600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>6754500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>6516700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>6909700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>6013100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>6558400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>6886000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>6639900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5756200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>5417700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>6222800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>5506100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>4950700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>5030600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>5466600</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>4992900</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>4232700</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>4518900</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>4969300</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>5027400</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>24095600</v>
+      </c>
+      <c r="E18" s="3">
         <v>20605600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>17961000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>16424500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>15846800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>12234200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>12987000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>11358800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>8820900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>7788400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>8492900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>7087200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>6479500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>7580100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>10176400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>9622800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>8306300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>7015500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>5739000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>5566200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>4724100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>4799200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>5009000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>5023500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>4389100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>4629300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>4433100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>3868700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2666700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2254500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>3649700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>3176500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>2808100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>3220500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>3529400</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>3177900</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>2698300</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>3109000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>3581900</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>3464400</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2040,618 +2072,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-179900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-85400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-35400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-48500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-277900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-55400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-53100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-111900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-47100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-30400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-124400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-47500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-70100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-82800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>406500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>302300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>215200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>162800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>132600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>136100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>157500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>168900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>151600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>182600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>191200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>149800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>184900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>189900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>178600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>168900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>164700</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>146400</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>126000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>130500</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>116900</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>107200</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>120000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>107600</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>98400</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>92400</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>30416400</v>
+      </c>
+      <c r="E21" s="3">
         <v>25773400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>23068900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>21721900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>22465900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>17478400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>18166300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>16696800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>13884900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>12718000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>13460900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>11641300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>10456700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>11210400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>13951300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>13191900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>12109600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>10661300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>9346400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>9186000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>8247900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>8184800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>8270900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>8377700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>6953200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>7248400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>7027400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>6452500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>5468200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>5143700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>6404700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>5777700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>5309100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>5729000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>5941400</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>5591600</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>4697800</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>5178800</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>5520800</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>5391800</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>97000</v>
+      </c>
+      <c r="E22" s="3">
         <v>85000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>96900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>97100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>126200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>80500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>77000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>83000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>81200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>84400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>95300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>96700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>96400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>97200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>104400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>104500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>92000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>67100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>68300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>43400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>36800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>24600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>24500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>12500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>13700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>19100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>23000</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>30200</v>
       </c>
       <c r="AE22" s="3">
         <v>30200</v>
       </c>
       <c r="AF22" s="3">
+        <v>30200</v>
+      </c>
+      <c r="AG22" s="3">
         <v>31500</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>29800</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>24600</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>20900</v>
-      </c>
-      <c r="AJ22" s="3">
-        <v>26900</v>
       </c>
       <c r="AK22" s="3">
         <v>26900</v>
       </c>
       <c r="AL22" s="3">
+        <v>26900</v>
+      </c>
+      <c r="AM22" s="3">
         <v>27300</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>27200</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>26600</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>26500</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>27107700</v>
+      </c>
+      <c r="E23" s="3">
         <v>21507200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>18863600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>17234300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>16859400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>12949900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>13691300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>12096200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>9429000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>8336500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>9087600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>7518300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>6887400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>8007400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>10478500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>9820600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>8429500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>7111200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>5803300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>5658900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>4844800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>4943500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>5136100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>5193600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>4566600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>4759900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>4594900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>4028400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2815100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2391800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>3784600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>3298200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>2913200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>3324100</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>3619400</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>3257800</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>2791100</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>3190000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>3653900</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>3530000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>4892300</v>
+      </c>
+      <c r="E24" s="3">
         <v>3595900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3414200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2414800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3267100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2108600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2722300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1861000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1805400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1292400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>876700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>967800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1057400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1223600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1214600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1107800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>913200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>751100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>579200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>565500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>483500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>488600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>582900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>594100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>519100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>543300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>453300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>402800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>481200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>238300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>377400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>326800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>508700</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>337800</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>400900</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>342500</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>643200</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>332700</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>385400</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>373700</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2772,252 +2820,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>22215300</v>
+      </c>
+      <c r="E26" s="3">
         <v>17911200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>15449400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>14819400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>13592300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>10841300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>10968900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>10235200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>7623600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>7044100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>8210900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>6550500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5830100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>6783900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>9264000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>8712800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>7516200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>6360100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>5224100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>5093400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>4361200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>4454900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>4553200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>4599400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>4047500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>4216600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>4141700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>3625500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2333800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2153500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>3407200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>2971400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>2404500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>2986300</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>3218500</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>2915300</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>2147800</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>2857300</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>3268400</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>3156300</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>22208500</v>
+      </c>
+      <c r="E27" s="3">
         <v>17901200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>15459700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>14837300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>13619000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>10866300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>10976000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>10240800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>7629300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>7052400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>8223600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>6556900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>5832700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>6785100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>9264800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>8709600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>7511400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>6355700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>5219700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>5086200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>4357300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>4453300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>4551400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>4597100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>4045100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>4213900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>4140100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>3624400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>2333400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>2153700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>3406500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>2970500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>2404400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>2986200</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>3217900</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>2914500</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>2147800</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>2857600</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>3267500</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>3155300</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3138,8 +3195,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3260,8 +3320,11 @@
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -3382,8 +3445,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -3504,252 +3570,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>179900</v>
+      </c>
+      <c r="E32" s="3">
         <v>85400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>35400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>48500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>277900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>55400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>53100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>111900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>47100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>30400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>124400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>47500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>70100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>82800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-406500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-302300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-215200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-162800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-132600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-136100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-157500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-168900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-151600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-182600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-191200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-149800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-184900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-189900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-178600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-168900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-164700</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-146400</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-126000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-130500</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-116900</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-107200</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-120000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-107600</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-98400</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-92400</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>22208500</v>
+      </c>
+      <c r="E33" s="3">
         <v>17901200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>15459700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>14837300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>13619000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>10866300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>10976000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>10240800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>7629300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>7052400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>8223600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>6556900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>5832700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>6785100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>9264800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>8709600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>7511400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>6355700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>5219700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>5086200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>4357300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>4453300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>4551400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>4597100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>4045100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>4213900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>4140100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>3624400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>2333400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>2153700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>3406500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>2970500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>2404400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>2986200</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>3217900</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>2914500</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>2147800</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>2857600</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>3267500</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>3155300</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3870,257 +3945,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>22208500</v>
+      </c>
+      <c r="E35" s="3">
         <v>17901200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>15459700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>14837300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>13619000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>10866300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>10976000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>10240800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>7629300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>7052400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>8223600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>6556900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>5832700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>6785100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>9264800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>8709600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>7511400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>6355700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>5219700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>5086200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>4357300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>4453300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>4551400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>4597100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>4045100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>4213900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>4140100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>3624400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>2333400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>2153700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>3406500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>2970500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>2404400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>2986200</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>3217900</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>2914500</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>2147800</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>2857600</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>3267500</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>3155300</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -4163,8 +4247,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -4207,1106 +4292,1134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>98513900</v>
+      </c>
+      <c r="E41" s="3">
         <v>94923000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>88142700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>81051000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>80855000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>71972200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>64906300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>59405600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>55381600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>53113400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>47830400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>40764700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>40961300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>45408500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>42043500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>40189400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>39713600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>36102300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>33440700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>27791600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>24257100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>21191500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>21046200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>20228500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>15655700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>15516600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>16248600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>16224200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>22706900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>22650100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>19686100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>16299200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>21028000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>19217100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>17935400</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>13225800</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>18488800</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>18415700</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>17650300</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>15130100</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>12063200</v>
+      </c>
+      <c r="E42" s="3">
         <v>10880500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>9573900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>9194200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>9169000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>9263300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>8974500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>8811000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>7680200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>7020300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>7230100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>7438400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>6813900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>6657400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>7659500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>7058800</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>6251400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>4590400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>4393600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>4425000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>4386000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>4687500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>4454400</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>4867200</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>4924400</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>5052000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>4951600</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>5379600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>4532100</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>4384600</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>4628600</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>4342600</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>4313700</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>3928700</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>3325800</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>3200600</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>2937600</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>3206500</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>3091300</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>1910300</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>13897000</v>
+      </c>
+      <c r="E43" s="3">
         <v>11403700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>8982200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>10099400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>8147100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7331500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>8300400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>7872800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6544800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6319700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6593500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6926900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>6209600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4855600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>7245400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>8112700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>7117200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>6692800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>6228600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>6094700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>5836500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>5340900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>4657300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>5444500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>5095000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>5276200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>4988900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>5216800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>4112700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3746200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>4404000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>4322300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>3039400</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>3589100</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>3969900</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>3853300</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>3625400</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>3559800</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>4221400</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>4221000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>12117700</v>
+      </c>
+      <c r="E44" s="3">
         <v>9739000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>9174900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>9470200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>10401900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>8817300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>8781800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>9221500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>8387900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>8354700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>8192300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>8144500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>7518100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>7082800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>6924200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>6770600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>6890600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>6273700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>6063400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>5931700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>5527300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>4927600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>4378800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>3666400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>2872200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>2819600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>2960800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>3467200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>3782700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>3812600</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>3517100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>3513000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>3293800</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>2834300</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>2394500</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>2394900</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>1977400</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>1643200</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>1587500</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>1757100</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>6916000</v>
+      </c>
+      <c r="E45" s="3">
         <v>6434400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5683300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2900500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3071000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3164500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3251500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2026200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1783200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1905600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1765200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1439000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1378800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1416500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>403600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>330000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>424200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>332900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>335800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>371300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>242200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>188900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>282100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>267000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>246600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>240500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>201000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>172700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>171400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>182200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>187900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>178000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>222900</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1333300</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>156400</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>170000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>132000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>99600</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>115600</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>121300</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>143507800</v>
+      </c>
+      <c r="E46" s="3">
         <v>133380600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>121556900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>112715400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>111644000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>100548900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>94214500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>87337100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>79777700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>76713700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>71611500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>64713400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>62881800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>65420800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>64276200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>62461300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>60396900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>53992100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>50462100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>44614300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>40249000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>36336400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>34818900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>34473500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>28793900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>28905000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>29350900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>30460500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>35305800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>34775700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>32423700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>28655100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>31897800</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>30902400</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>27782000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>22844600</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>27161200</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>26924800</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>26666100</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>23139800</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>7164400</v>
+      </c>
+      <c r="E47" s="3">
         <v>5208500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>5483400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>4887100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>4699300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>4832400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>4541400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>4009100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4316300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4330800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>4219200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>3615500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>3035400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2291800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2158100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2350400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2042100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1433900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>922700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>902600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>942500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>928700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>884000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>887700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>767300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1117800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1076500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1080600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1024600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1053800</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>998400</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>993900</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>959100</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>1143400</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>1347300</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>1325700</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>1420200</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>1451800</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>1505100</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>1627600</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>136972400</v>
+      </c>
+      <c r="E48" s="3">
         <v>125098300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>118965700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>116212100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>117291200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>103447400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>99911800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>97959700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>96822400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>96706100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>101341500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>98630200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>95891100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>94257400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>85656400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>76093600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>72336000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>67002900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>63046600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>60603400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>56924300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>53903800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>50476200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>51065800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>50708700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>52586900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>48867700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>43586500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>40573900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>39524500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>36524800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>34968000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>34399800</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>35101500</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>34437000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>34541200</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>34925900</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>33828400</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>32537500</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>30488000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>756700</v>
+      </c>
+      <c r="E49" s="3">
         <v>773300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>794600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>838400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>844900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>764900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>801800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>695300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>690500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>695600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>743100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>727500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>765200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>796500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>814000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>828200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>862300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>803200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>842200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>834700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>860500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>797400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>821500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>881800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>917200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>980900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>736900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>648800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>611700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>630500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>579300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>466500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>458700</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>454800</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>459400</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>481000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>457600</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>465600</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>476600</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>477100</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -5427,8 +5540,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -5549,130 +5665,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>4314900</v>
+      </c>
+      <c r="E52" s="3">
         <v>4320500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3817300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4554800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2880500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2783100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2660500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2049300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>539400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>584900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>556600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>539800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>443800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>384000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2542500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2255300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2085600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1938300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1707200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1511700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1323600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1095600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1011000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>930100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>794200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>814900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>776300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>757200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>749100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>750900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>684500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>612200</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>581200</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>552800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>530600</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>488100</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>415500</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>418700</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>332000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>313900</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -5793,130 +5915,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>294692900</v>
+      </c>
+      <c r="E54" s="3">
         <v>270823900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>252622200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>241244800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>239582500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>214380200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>204141700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>194126700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>184152100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>181024300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>180566500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>170433700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>165211100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>165405000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>155447200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>143988800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>137722900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>125170400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>116980800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>108466800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>100300000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>93061900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>88011500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>88239000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>81981300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>84405500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>80808200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>76533600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>78265100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>76735300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>71210700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>65695800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>68296500</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>68154900</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>64556200</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>59680600</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>64380300</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>63089400</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>61517300</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>56046400</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -5959,8 +6087,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -6003,740 +6132,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>3474200</v>
+      </c>
+      <c r="E57" s="3">
         <v>3119200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2682100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2829000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2894400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2306900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2260400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2225800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1966400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1797500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1867100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1668200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1570100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1552700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1769700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1923200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1895600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1570800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1529900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1428600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1337100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1230500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1310100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1369100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1323600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1432700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1434500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1325300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1138300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>970400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1170600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1010700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1019900</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>965900</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>974500</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>939500</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>830100</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>790900</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>891100</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>847100</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>5375400</v>
+      </c>
+      <c r="E58" s="3">
         <v>4998200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4482500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2620400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3349100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1951200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1919100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1942800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>791100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>483100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1287200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1152100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>577500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>351600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>686200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>806000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>4274500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>5126600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3820300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3935900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>4580500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>4432000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2964400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>5346700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>6388800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>5670400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>5444700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>4301600</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>4510200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>4468900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>4212900</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>3631000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1554400</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>3528500</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>3959500</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>3678600</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>4362700</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>3247200</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>3132800</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>2470500</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>34948400</v>
+      </c>
+      <c r="E59" s="3">
         <v>32710400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>32143100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>25081000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>27556600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>27795900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>29307900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>21591800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>21141700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>22643600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>21996200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>21579600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>16714200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>19957100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>27107800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>22309300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>20615600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>19099500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>17870200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>15976000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>15088900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>15430900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>15400200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>12978600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>12870900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>14129500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>14198200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>12116000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>16099400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>7830300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>6218800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>6084700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>12825000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>6888300</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>6691700</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>5057000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>11774100</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>6448700</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>6354000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>5081300</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>58392600</v>
+      </c>
+      <c r="E60" s="3">
         <v>53603900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>48481400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>41855000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>47097300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>42069000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>39922400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>34016500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>32288200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>32095200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>30772400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>30144000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>26014000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>28620300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>29563700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>25038400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>26785700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>25796900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>23220400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>21340500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>21006500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>21093400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>19674800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>19694300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>20583400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>21232600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>21077400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>17742900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>21747900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>13269600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>11602300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>10726400</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>15399300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>11382700</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>11625700</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>9675100</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>16966900</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>10486700</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>10377800</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>8398900</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>28211200</v>
+      </c>
+      <c r="E61" s="3">
         <v>29222200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>29541300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>31137900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>31289700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>30537500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>30115400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>30363400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>30861500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>31089600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>30908200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>30046900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>30063700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>29003100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>27204000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>27153100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>24709300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>20496800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>19912100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>15762600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>14096200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>9581100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>8819100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>8276500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>3401700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2376100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1432300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1439100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1772200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1831400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1938600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1897600</v>
-      </c>
-      <c r="AI61" s="3">
-        <v>2773900</v>
       </c>
       <c r="AJ61" s="3">
         <v>2773900</v>
       </c>
       <c r="AK61" s="3">
+        <v>2773900</v>
+      </c>
+      <c r="AL61" s="3">
         <v>2975200</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>2975700</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>3218900</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>4376900</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>4993100</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>4962000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>4277300</v>
+      </c>
+      <c r="E62" s="3">
         <v>2187600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2441000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2760400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3011200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3197900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3205700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2871400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3169800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2947000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5850600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5157500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>6003800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>6089200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5986600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>6447900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>6671400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>6098700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>5687300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3714300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>532800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>508500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>519800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>396900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>370000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>390200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>422200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>424000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>418000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>471600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>517500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>517900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>544800</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>562600</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>602700</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>637700</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>688500</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>735500</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>816900</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>817700</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -6857,8 +7005,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6979,8 +7130,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -7101,130 +7255,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>91189200</v>
+      </c>
+      <c r="E66" s="3">
         <v>85320800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>80779000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>76057300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>81716500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>76085300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>73596500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>67495900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>66558400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>66374000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>67835000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>65622700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>62369600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>64018400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>63218800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>59084200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>58613400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>52613000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>48896600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>40892300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>35706400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>31248600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>29044400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>28398100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>24383000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>24026400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>22956300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>19629000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>23959200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>15596300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>14081500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>13163800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>18739100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>14742700</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>15226400</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>13311000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>20896300</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>15625100</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>16213900</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>14204100</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -7267,8 +7427,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -7389,8 +7550,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -7511,8 +7675,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -7633,8 +7800,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -7755,130 +7925,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>190196900</v>
+      </c>
+      <c r="E72" s="3">
         <v>172623200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>160465700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>155935300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>151514400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>125091000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>118150500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>115153200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>105851000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>103042100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>102116300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>93552900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>92313200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>90909600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>82580900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>74820100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>69817100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>63899500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>59874500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>58957000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>55984600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>53025100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>50647300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>50687900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>48261200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>49905600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>47573400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>45969200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>43532900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>50443200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>46902400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>42612600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>39561800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>44059200</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>39973300</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>36763300</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>33848900</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>37815800</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>34958200</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>31721600</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -7999,8 +8175,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -8121,8 +8300,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -8243,130 +8425,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>202185100</v>
+      </c>
+      <c r="E76" s="3">
         <v>184207600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>170531800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>163964900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>156650000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>137169000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>129477300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>125626400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>116708800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>113712600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>111936900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>104050600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>102305200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>100905900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>92228400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>84904600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>79109400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>72557400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>68084200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>67574500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>64593600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>61813300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>58967100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>59840800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>57598300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>60379100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>57851900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>56904700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>54305800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>61139000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>57129200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>52532000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>49557500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>53412200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>49329900</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>46369500</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>43484000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>47464300</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>45303400</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>41842300</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -8487,257 +8675,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>22208500</v>
+      </c>
+      <c r="E81" s="3">
         <v>17901200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>15459700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>14837300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>13619000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>10866300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>10976000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>10240800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>7629300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>7052400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>8223600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>6556900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>5832700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>6785100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>9264800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>8709600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>7511400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>6355700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>5219700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>5086200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>4357300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>4453300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>4551400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>4597100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>4045100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>4213900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>4140100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>3624400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>2333400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>2153700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>3406500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>2970500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>2404400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>2986200</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>3217900</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>2914500</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>2147800</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>2857600</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>3267500</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>3155300</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -8780,130 +8977,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>6360500</v>
+      </c>
+      <c r="E83" s="3">
         <v>5199400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>5127200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>5223900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>5015400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4900900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4839700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4503600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3902700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3543000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3430100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3244700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>3731700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>3802600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>3368400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>3266800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>3588100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>3483000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>3474800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>3483700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>3366400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>3216700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>3110300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>3171700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>2372900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>2469300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>2409500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>2393900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>2622900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>2720400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>2590300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>2454900</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>2375100</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>2378000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>2295100</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>2306400</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>1879500</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>1962200</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>1840400</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>1834900</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -9024,8 +9225,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -9146,8 +9350,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -9268,8 +9475,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -9390,8 +9600,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -9512,130 +9725,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>24622500</v>
+      </c>
+      <c r="E89" s="3">
         <v>21856700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>23103900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>14001700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>16997100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>18800700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>18920200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>12341900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>11625600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>13646200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>12886900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>9156200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>5365800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>12628500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>15244300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>12797800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>10738100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>11667500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>11875500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>10373900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>6078700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>7262800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>8261100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>6366900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>5702800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>7313100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>7241400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>5083300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>4115700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>5355700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>6451900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>3137700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>4316300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>5345700</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>6615700</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>3785000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>3351200</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>5250500</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>6040000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>4122200</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -9678,130 +9897,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-15590200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-10968200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-11365700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-9429600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-10163700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-9942500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-11041700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-6519900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-6331200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5670600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5553900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-7042400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-8037900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-9916000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-338327600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-267635800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-220945300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-262717700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-238919200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-190193800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-5414900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-7907200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2827000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-3324800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-4241900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-6936000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-6065900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-3518500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-4066500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-2664000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-3887600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-2332800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-1985000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-2389600</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-1982800</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-2000200</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-3409200</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-3372600</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-3710900</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-3423400</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -9922,8 +10145,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -10044,130 +10270,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-15489900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-11158700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-11654000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-8520900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-7813200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-8721300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-9515500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-6155700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-6082800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4998200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4318800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-7527800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-8320000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-8923900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-10724700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-8818900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-8744300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-9031100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-7703800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-5762000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-5505000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-7786700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2899800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-3216700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-4344000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-6807500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-6122900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-3883300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-4009400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2251700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-3995100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-2116800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1998100</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-2443300</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-2043500</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-2128100</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-3183300</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-3562000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-4516500</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-3485500</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -10210,92 +10442,93 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>4890600</v>
+      </c>
+      <c r="E96" s="3">
         <v>4054500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>4129100</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>3828100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>3990500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>3117200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>3164600</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>2857700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>2793900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>2433200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>2539200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>2215900</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>2287800</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>2337500</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-2232700</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-2211300</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-2259800</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-2235500</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-2239100</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-2110100</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-2102300</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-2066700</v>
       </c>
       <c r="Y96" s="3">
         <v>-2066700</v>
       </c>
       <c r="Z96" s="3">
-        <v>-2170400</v>
+        <v>-2066700</v>
       </c>
       <c r="AA96" s="3">
         <v>-2170400</v>
       </c>
       <c r="AB96" s="3">
+        <v>-2170400</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-2335000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-1850400</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
         <v>0</v>
       </c>
@@ -10332,8 +10565,11 @@
       <c r="AP96" s="3">
         <v>0</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -10454,8 +10690,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -10576,8 +10815,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -10698,370 +10940,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-5804000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3749600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3429200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-4208500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4093200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2544500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3073000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2633400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2778000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2242100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2459900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1194900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-853100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2113900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2186400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-4043900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>604700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-598400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2583700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1149800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>2433200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>466000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-3226400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>1588100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>197900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1468100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-613100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-8216000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-32500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-786200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>486600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-5750700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-976100</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-1916700</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>312600</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-6896600</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-20700</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-388400</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>792500</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-5517300</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>-6126200</v>
+      </c>
+      <c r="E101" s="3">
         <v>494700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1015600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-793100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>342200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>874200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1094100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>656700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>325900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-200200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-902200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1413100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>658800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>753600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-867800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>1393000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>621200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>676800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-124400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-17300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-306900</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>203200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-350400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-165500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-323400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>75600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-399500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-58000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>66900</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>62700</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>91600</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-55800</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>468800</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-174600</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-175200</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-23200</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>38900</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-534700</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>204200</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-284400</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>3098600</v>
+      </c>
+      <c r="E102" s="3">
         <v>8373400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>9461100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3484900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1035400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>8029600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>7347400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2759800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>3106900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>7280100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>5014100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1090200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3481300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1390500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1465300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1328000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>3219700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>2714900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>6631000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>3444800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>2699900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>145300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1784500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>4572800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1233300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-886900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>105900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-7074000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>140700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>2380400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>3035000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-4785700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1810900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>811300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>4709600</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-5263000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>186100</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>765400</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>2520200</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-5165000</v>
       </c>
     </row>
